--- a/backend/data/users.xlsx
+++ b/backend/data/users.xlsx
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Telegram_Project\Orange-Flow-Next-Js\backend\_data_list\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\sadekinislam\projects\Orange-Flow-Next-Js\backend\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DB1E899-A9E0-408D-8B0E-8652858778A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64822A57-91B4-4041-8333-A7EBBC8404BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{BB0F9CCB-0FBE-4AFF-BD3B-D4E64BAEDA77}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BB0F9CCB-0FBE-4AFF-BD3B-D4E64BAEDA77}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$47</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="115">
   <si>
     <t xml:space="preserve"> TELEGRAM_ID</t>
   </si>
@@ -387,33 +387,6 @@
   </si>
   <si>
     <t>nurunnabi</t>
-  </si>
-  <si>
-    <t>Inactive</t>
-  </si>
-  <si>
-    <t>Safiqul Islam</t>
-  </si>
-  <si>
-    <t>shafiqulislam</t>
-  </si>
-  <si>
-    <t>Md. Golam Mostufa</t>
-  </si>
-  <si>
-    <t>golammostofa</t>
-  </si>
-  <si>
-    <t>Riaz Ahmed</t>
-  </si>
-  <si>
-    <t>riazahmed</t>
-  </si>
-  <si>
-    <t>Opi Ahmed Shuvo</t>
-  </si>
-  <si>
-    <t>opiahmed</t>
   </si>
 </sst>
 </file>
@@ -803,7 +776,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B226F8CE-143F-43E3-8E7D-9AF252188EC1}">
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr defaultColWidth="13.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -1971,98 +1944,6 @@
         <v>7</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B48" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="E48" s="1">
-        <v>1642536878</v>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H48" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="I48" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="49" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B49" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="E49" s="1">
-        <v>1975607780</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H49" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="I49" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="50" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B50" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="E50" s="1">
-        <v>1911000000</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G50" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="H50" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="I50" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="51" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B51" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="E51" s="1">
-        <v>1911000001</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G51" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="H51" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="I51" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/backend/data/users.xlsx
+++ b/backend/data/users.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\sadekinislam\projects\Orange-Flow-Next-Js\backend\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\emil\projects\Orange-Flow-Next-Js\backend\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64822A57-91B4-4041-8333-A7EBBC8404BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EB163B9-4B70-48E6-8061-62F61077F015}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BB0F9CCB-0FBE-4AFF-BD3B-D4E64BAEDA77}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{BB0F9CCB-0FBE-4AFF-BD3B-D4E64BAEDA77}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="120">
   <si>
     <t xml:space="preserve"> TELEGRAM_ID</t>
   </si>
@@ -387,6 +387,21 @@
   </si>
   <si>
     <t>nurunnabi</t>
+  </si>
+  <si>
+    <t>Inactive</t>
+  </si>
+  <si>
+    <t>Soliman</t>
+  </si>
+  <si>
+    <t>soliman</t>
+  </si>
+  <si>
+    <t>Arif</t>
+  </si>
+  <si>
+    <t>arif</t>
   </si>
 </sst>
 </file>
@@ -776,7 +791,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B226F8CE-143F-43E3-8E7D-9AF252188EC1}">
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr defaultColWidth="13.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -1757,7 +1772,7 @@
         <v>33</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>7</v>
+        <v>115</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
@@ -1780,7 +1795,7 @@
         <v>33</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>7</v>
+        <v>115</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
@@ -1895,7 +1910,7 @@
         <v>33</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>7</v>
+        <v>115</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
@@ -1941,6 +1956,52 @@
         <v>33</v>
       </c>
       <c r="I47" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B48" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E48" s="1">
+        <v>1410167293</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="49" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B49" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E49" s="1">
+        <v>1410449332</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I49" s="1" t="s">
         <v>7</v>
       </c>
     </row>

--- a/backend/data/users.xlsx
+++ b/backend/data/users.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\emil\projects\Orange-Flow-Next-Js\backend\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EB163B9-4B70-48E6-8061-62F61077F015}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{478170B8-BCE0-4B1D-8234-F380B8F4AD10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{BB0F9CCB-0FBE-4AFF-BD3B-D4E64BAEDA77}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BB0F9CCB-0FBE-4AFF-BD3B-D4E64BAEDA77}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$50</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="122">
   <si>
     <t xml:space="preserve"> TELEGRAM_ID</t>
   </si>
@@ -402,6 +402,12 @@
   </si>
   <si>
     <t>arif</t>
+  </si>
+  <si>
+    <t>Ruhul Amin</t>
+  </si>
+  <si>
+    <t>ruhulamin</t>
   </si>
 </sst>
 </file>
@@ -791,13 +797,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B226F8CE-143F-43E3-8E7D-9AF252188EC1}">
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr defaultColWidth="13.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="29.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -837,23 +843,23 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <v>8704561358</v>
+        <v>8217920077</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="1">
-        <v>1917747555</v>
+        <v>1912317878</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>33</v>
@@ -864,23 +870,23 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
-        <v>8759226993</v>
+        <v>8251541258</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="1">
-        <v>1918537111</v>
+        <v>1911626293</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>33</v>
@@ -890,24 +896,21 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>8474847602</v>
-      </c>
       <c r="B4" s="1" t="s">
-        <v>9</v>
+        <v>87</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>40</v>
+        <v>89</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="1">
-        <v>1911229913</v>
+        <v>1935597976</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>33</v>
@@ -917,24 +920,21 @@
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>8217920077</v>
-      </c>
       <c r="B5" s="1" t="s">
-        <v>5</v>
+        <v>88</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>41</v>
+        <v>90</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="1">
-        <v>1912317878</v>
+        <v>1935597774</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>6</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>33</v>
@@ -944,24 +944,21 @@
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>8251541258</v>
-      </c>
       <c r="B6" s="1" t="s">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>42</v>
+        <v>93</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="1">
-        <v>1911626293</v>
+        <v>1999968844</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>6</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>33</v>
@@ -972,20 +969,20 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="1">
-        <v>1935597976</v>
+        <v>1935600928</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>6</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>23</v>
+        <v>67</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>33</v>
@@ -995,21 +992,24 @@
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>8980795758</v>
+      </c>
       <c r="B8" s="1" t="s">
-        <v>88</v>
+        <v>28</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>90</v>
+        <v>48</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="1">
-        <v>1935597774</v>
+        <v>1410240211</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>33</v>
@@ -1020,20 +1020,19 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B9" s="1" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="D9" s="2"/>
+        <v>97</v>
+      </c>
       <c r="E9" s="1">
-        <v>1999968844</v>
+        <v>1410678746</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>67</v>
+        <v>25</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>33</v>
@@ -1044,44 +1043,39 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="D10" s="2"/>
+        <v>98</v>
+      </c>
       <c r="E10" s="1">
-        <v>1935600928</v>
+        <v>1410071973</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>67</v>
+        <v>25</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>33</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>7</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
-        <v>6287137090</v>
-      </c>
       <c r="B11" s="1" t="s">
-        <v>17</v>
+        <v>99</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D11" s="2"/>
+        <v>107</v>
+      </c>
       <c r="E11" s="1">
-        <v>1976466262</v>
+        <v>1410436602</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>25</v>
@@ -1090,22 +1084,18 @@
         <v>33</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>7</v>
+        <v>115</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
-        <v>8980795758</v>
-      </c>
       <c r="B12" s="1" t="s">
-        <v>28</v>
+        <v>100</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D12" s="2"/>
+        <v>108</v>
+      </c>
       <c r="E12" s="1">
-        <v>1410240211</v>
+        <v>1410213723</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>22</v>
@@ -1122,20 +1112,19 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
-        <v>53</v>
+        <v>101</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D13" s="2"/>
+        <v>109</v>
+      </c>
       <c r="E13" s="1">
-        <v>1403238887</v>
+        <v>1410173774</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>67</v>
+        <v>25</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>33</v>
@@ -1146,19 +1135,19 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B14" s="1" t="s">
-        <v>54</v>
+        <v>102</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>61</v>
+        <v>110</v>
       </c>
       <c r="E14" s="1">
-        <v>1747736930</v>
+        <v>1410720313</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>67</v>
+        <v>25</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>33</v>
@@ -1169,19 +1158,19 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B15" s="1" t="s">
-        <v>55</v>
+        <v>103</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>64</v>
+        <v>111</v>
       </c>
       <c r="E15" s="1">
-        <v>1540066110</v>
+        <v>1410031485</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>67</v>
+        <v>25</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>33</v>
@@ -1192,65 +1181,65 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B16" s="1" t="s">
-        <v>56</v>
+        <v>104</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>62</v>
+        <v>112</v>
       </c>
       <c r="E16" s="1">
-        <v>1747736930</v>
+        <v>1410284216</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>67</v>
+        <v>25</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>33</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>7</v>
+        <v>115</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B17" s="1" t="s">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>65</v>
+        <v>114</v>
       </c>
       <c r="E17" s="1">
-        <v>1402026262</v>
+        <v>1410589082</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>67</v>
+        <v>25</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>33</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>7</v>
+        <v>115</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B18" s="1" t="s">
-        <v>58</v>
+        <v>116</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>66</v>
+        <v>117</v>
       </c>
       <c r="E18" s="1">
-        <v>1911055218</v>
+        <v>1410167293</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>67</v>
+        <v>25</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>33</v>
@@ -1261,19 +1250,19 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
-        <v>59</v>
+        <v>118</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>63</v>
+        <v>119</v>
       </c>
       <c r="E19" s="1">
-        <v>1936792109</v>
+        <v>1410449332</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>67</v>
+        <v>25</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>33</v>
@@ -1283,20 +1272,24 @@
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>8704561358</v>
+      </c>
       <c r="B20" s="1" t="s">
-        <v>68</v>
+        <v>15</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>77</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="D20" s="2"/>
       <c r="E20" s="1">
-        <v>1911229913</v>
+        <v>1917747555</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>33</v>
@@ -1306,20 +1299,24 @@
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>8759226993</v>
+      </c>
       <c r="B21" s="1" t="s">
-        <v>69</v>
+        <v>11</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>79</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="D21" s="2"/>
       <c r="E21" s="1">
-        <v>1947145899</v>
+        <v>1918537111</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>33</v>
@@ -1330,22 +1327,23 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
-        <v>6857806283</v>
+        <v>6287137090</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>70</v>
+        <v>17</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>83</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="D22" s="2"/>
       <c r="E22" s="1">
-        <v>1831949395</v>
+        <v>1976466262</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>33</v>
@@ -1355,23 +1353,21 @@
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="1">
-        <v>8681308050</v>
-      </c>
       <c r="B23" s="1" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>44</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="D23" s="2"/>
       <c r="E23" s="1">
-        <v>1908441954</v>
+        <v>1403238887</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>23</v>
+        <v>67</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>33</v>
@@ -1381,23 +1377,20 @@
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="1">
-        <v>7586404983</v>
-      </c>
       <c r="B24" s="1" t="s">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="E24" s="1">
-        <v>1984220365</v>
+        <v>1747736930</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>23</v>
+        <v>67</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>33</v>
@@ -1407,23 +1400,20 @@
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="1">
-        <v>8273936271</v>
-      </c>
       <c r="B25" s="1" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="E25" s="1">
-        <v>1984220366</v>
+        <v>1540066110</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>23</v>
+        <v>67</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>33</v>
@@ -1433,23 +1423,20 @@
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="1">
-        <v>7891698602</v>
-      </c>
       <c r="B26" s="1" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="E26" s="1">
-        <v>1620502971</v>
+        <v>1747736930</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>23</v>
+        <v>67</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>33</v>
@@ -1460,19 +1447,19 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B27" s="1" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="E27" s="1">
-        <v>1747736930</v>
+        <v>1402026262</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>23</v>
+        <v>67</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>33</v>
@@ -1482,23 +1469,20 @@
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="1">
-        <v>7224463249</v>
-      </c>
       <c r="B28" s="1" t="s">
-        <v>19</v>
+        <v>58</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="E28" s="1">
-        <v>1917509966</v>
+        <v>1911055218</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>23</v>
+        <v>67</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>33</v>
@@ -1508,23 +1492,20 @@
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="1">
-        <v>7479560514</v>
-      </c>
       <c r="B29" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="E29" s="1">
-        <v>1775222954</v>
+        <v>1936792109</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>23</v>
+        <v>67</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>33</v>
@@ -1535,13 +1516,13 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B30" s="1" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="E30" s="1">
-        <v>1617451080</v>
+        <v>1911229913</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>13</v>
@@ -1558,13 +1539,13 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B31" s="1" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E31" s="1">
-        <v>1747736930</v>
+        <v>1947145899</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>13</v>
@@ -1581,16 +1562,16 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
-        <v>6534313772</v>
+        <v>6857806283</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E32" s="1">
-        <v>1322159543</v>
+        <v>1831949395</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>13</v>
@@ -1607,16 +1588,16 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
-        <v>6519999519</v>
+        <v>8681308050</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E33" s="1">
-        <v>1997616187</v>
+        <v>1908441954</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>13</v>
@@ -1633,16 +1614,16 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
-        <v>8434757540</v>
+        <v>7586404983</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="E34" s="1">
-        <v>1924303333</v>
+        <v>1984220365</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>13</v>
@@ -1658,14 +1639,17 @@
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
+        <v>8273936271</v>
+      </c>
       <c r="B35" s="1" t="s">
-        <v>75</v>
+        <v>21</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="E35" s="1">
-        <v>1935591914</v>
+        <v>1984220366</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>13</v>
@@ -1682,16 +1666,16 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
-        <v>6594315783</v>
+        <v>7891698602</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>86</v>
+        <v>49</v>
       </c>
       <c r="E36" s="1">
-        <v>1813862410</v>
+        <v>1620502971</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>13</v>
@@ -1708,13 +1692,13 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B37" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E37" s="1">
-        <v>1401607080</v>
+        <v>1747736930</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>13</v>
@@ -1730,20 +1714,23 @@
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
+        <v>7224463249</v>
+      </c>
       <c r="B38" s="1" t="s">
-        <v>95</v>
+        <v>19</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>97</v>
+        <v>46</v>
       </c>
       <c r="E38" s="1">
-        <v>1410678746</v>
+        <v>1917509966</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H38" s="1" t="s">
         <v>33</v>
@@ -1753,66 +1740,69 @@
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
+        <v>7479560514</v>
+      </c>
       <c r="B39" s="1" t="s">
-        <v>96</v>
+        <v>36</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>98</v>
+        <v>50</v>
       </c>
       <c r="E39" s="1">
-        <v>1410071973</v>
+        <v>1775222954</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H39" s="1" t="s">
         <v>33</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>115</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B40" s="1" t="s">
-        <v>99</v>
+        <v>73</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="E40" s="1">
-        <v>1410436602</v>
+        <v>1617451080</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H40" s="1" t="s">
         <v>33</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>115</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B41" s="1" t="s">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>108</v>
+        <v>80</v>
       </c>
       <c r="E41" s="1">
-        <v>1410213723</v>
+        <v>1747736930</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H41" s="1" t="s">
         <v>33</v>
@@ -1822,20 +1812,23 @@
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A42" s="1">
+        <v>6534313772</v>
+      </c>
       <c r="B42" s="1" t="s">
-        <v>101</v>
+        <v>29</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="E42" s="1">
-        <v>1410173774</v>
+        <v>1322159543</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H42" s="1" t="s">
         <v>33</v>
@@ -1845,20 +1838,23 @@
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A43" s="1">
+        <v>6519999519</v>
+      </c>
       <c r="B43" s="1" t="s">
-        <v>102</v>
+        <v>37</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>110</v>
+        <v>47</v>
       </c>
       <c r="E43" s="1">
-        <v>1410720313</v>
+        <v>1997616187</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H43" s="1" t="s">
         <v>33</v>
@@ -1868,20 +1864,23 @@
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A44" s="1">
+        <v>8434757540</v>
+      </c>
       <c r="B44" s="1" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>111</v>
+        <v>43</v>
       </c>
       <c r="E44" s="1">
-        <v>1410031485</v>
+        <v>1924303333</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H44" s="1" t="s">
         <v>33</v>
@@ -1892,42 +1891,45 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B45" s="1" t="s">
-        <v>104</v>
+        <v>75</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>112</v>
+        <v>81</v>
       </c>
       <c r="E45" s="1">
-        <v>1410284216</v>
+        <v>1935591914</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H45" s="1" t="s">
         <v>33</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>115</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A46" s="1">
+        <v>6594315783</v>
+      </c>
       <c r="B46" s="1" t="s">
-        <v>105</v>
+        <v>34</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="E46" s="1">
-        <v>1918580928</v>
+        <v>1813862410</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H46" s="1" t="s">
         <v>33</v>
@@ -1938,42 +1940,46 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B47" s="1" t="s">
-        <v>106</v>
+        <v>76</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>114</v>
+        <v>82</v>
       </c>
       <c r="E47" s="1">
-        <v>1410589082</v>
+        <v>1401607080</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H47" s="1" t="s">
         <v>33</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>115</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A48" s="1">
+        <v>8474847602</v>
+      </c>
       <c r="B48" s="1" t="s">
-        <v>116</v>
+        <v>9</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>117</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="D48" s="2"/>
       <c r="E48" s="1">
-        <v>1410167293</v>
+        <v>1911229913</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H48" s="1" t="s">
         <v>33</v>
@@ -1984,28 +1990,57 @@
     </row>
     <row r="49" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B49" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>119</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="D49" s="2"/>
       <c r="E49" s="1">
-        <v>1410449332</v>
+        <v>1911266077</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G49" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="50" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B50" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E50" s="1">
+        <v>1918580928</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G50" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="H49" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="I49" s="1" t="s">
+      <c r="H50" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I50" s="1" t="s">
         <v>7</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:I50" xr:uid="{B226F8CE-143F-43E3-8E7D-9AF252188EC1}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I50">
+      <sortCondition ref="F1:F50"/>
+    </sortState>
+  </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
